--- a/data/trans_orig/P26-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P26-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2007</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67244</t>
+          <t>67728</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97201</t>
+          <t>96880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84049</t>
+          <t>84932</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114373</t>
+          <t>115499</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160518</t>
+          <t>158513</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203854</t>
+          <t>202651</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>146398</t>
+          <t>146719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176355</t>
+          <t>175871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116845</t>
+          <t>115719</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147169</t>
+          <t>146286</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>270964</t>
+          <t>272167</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>314300</t>
+          <t>316305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98962</t>
+          <t>100270</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>137435</t>
+          <t>137597</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134353</t>
+          <t>137490</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>177316</t>
+          <t>176753</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>244897</t>
+          <t>246619</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>302913</t>
+          <t>302961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>330284</t>
+          <t>330122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>368757</t>
+          <t>367449</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>285249</t>
+          <t>285812</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328212</t>
+          <t>325075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>627371</t>
+          <t>627323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>685387</t>
+          <t>683665</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,49%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65512</t>
+          <t>66865</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96471</t>
+          <t>97210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>101208</t>
+          <t>100651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133768</t>
+          <t>134361</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176495</t>
+          <t>175375</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>219735</t>
+          <t>220500</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>202005</t>
+          <t>201266</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>232964</t>
+          <t>231611</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171034</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>203594</t>
+          <t>204151</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>383543</t>
+          <t>382778</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>426783</t>
+          <t>427903</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81763</t>
+          <t>80590</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>114270</t>
+          <t>113919</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>124296</t>
+          <t>126051</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160029</t>
+          <t>160352</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>215481</t>
+          <t>214589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>264490</t>
+          <t>265910</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225016</t>
+          <t>225367</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>257523</t>
+          <t>258696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>179249</t>
+          <t>178926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>214982</t>
+          <t>213227</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>414073</t>
+          <t>412653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>463082</t>
+          <t>463974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39197</t>
+          <t>39008</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63516</t>
+          <t>63376</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44655</t>
+          <t>44945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70193</t>
+          <t>72442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89255</t>
+          <t>90749</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>125046</t>
+          <t>126269</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115746</t>
+          <t>115886</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140065</t>
+          <t>140254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117258</t>
+          <t>115009</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142796</t>
+          <t>142506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>241667</t>
+          <t>240444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>277458</t>
+          <t>275964</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57413</t>
+          <t>56843</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85957</t>
+          <t>85124</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83923</t>
+          <t>83155</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>114862</t>
+          <t>112461</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148293</t>
+          <t>148273</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>189964</t>
+          <t>186597</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,41%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>164878</t>
+          <t>165711</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193422</t>
+          <t>193992</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>133045</t>
+          <t>135446</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>163984</t>
+          <t>164752</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>308779</t>
+          <t>312146</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>350450</t>
+          <t>350470</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>153231</t>
+          <t>153572</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197271</t>
+          <t>198236</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>202339</t>
+          <t>203097</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>247219</t>
+          <t>250512</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>368505</t>
+          <t>369716</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>435949</t>
+          <t>437746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,58%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>379733</t>
+          <t>378768</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>423773</t>
+          <t>423432</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>340654</t>
+          <t>337361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>385534</t>
+          <t>384776</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>728928</t>
+          <t>727131</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>796372</t>
+          <t>795161</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>172163</t>
+          <t>174220</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>221507</t>
+          <t>224953</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>225287</t>
+          <t>226419</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>280136</t>
+          <t>280556</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>419005</t>
+          <t>415450</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>487861</t>
+          <t>486779</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>474177</t>
+          <t>470731</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>523521</t>
+          <t>521464</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>451157</t>
+          <t>450737</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>506006</t>
+          <t>504874</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>939116</t>
+          <t>940198</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1007972</t>
+          <t>1011527</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,89%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>819766</t>
+          <t>824973</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>919521</t>
+          <t>926295</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1092109</t>
+          <t>1093745</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1200621</t>
+          <t>1202815</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1943595</t>
+          <t>1943490</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2094258</t>
+          <t>2096193</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2132345</t>
+          <t>2125571</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2232100</t>
+          <t>2226893</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1891766</t>
+          <t>1889572</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2000278</t>
+          <t>1998642</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4049995</t>
+          <t>4048060</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4200658</t>
+          <t>4200763</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2012</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2012 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91793</t>
+          <t>91407</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125949</t>
+          <t>125762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100191</t>
+          <t>100738</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135621</t>
+          <t>135562</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>199245</t>
+          <t>200242</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>249956</t>
+          <t>252208</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,2%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>154970</t>
+          <t>155157</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189126</t>
+          <t>189512</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141495</t>
+          <t>141554</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176925</t>
+          <t>176378</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>308079</t>
+          <t>305827</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>358790</t>
+          <t>357793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,12%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>137224</t>
+          <t>138696</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>182526</t>
+          <t>185039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>185748</t>
+          <t>187018</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>231157</t>
+          <t>234038</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>339110</t>
+          <t>341742</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>401947</t>
+          <t>404881</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310761</t>
+          <t>308248</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>356063</t>
+          <t>354591</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>279865</t>
+          <t>276984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>325274</t>
+          <t>324004</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>602362</t>
+          <t>599428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>665199</t>
+          <t>662567</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,97%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92742</t>
+          <t>93215</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124485</t>
+          <t>125769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91604</t>
+          <t>93523</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128057</t>
+          <t>126685</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194495</t>
+          <t>194692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>243257</t>
+          <t>241174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>179127</t>
+          <t>177843</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>210870</t>
+          <t>210397</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>178313</t>
+          <t>179685</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>214766</t>
+          <t>212847</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>366725</t>
+          <t>368808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>415487</t>
+          <t>415290</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,08%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87501</t>
+          <t>89712</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128312</t>
+          <t>126622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>92140</t>
+          <t>94487</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128004</t>
+          <t>130342</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>194566</t>
+          <t>193573</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>244662</t>
+          <t>244953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238321</t>
+          <t>240011</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>279132</t>
+          <t>276921</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249488</t>
+          <t>247150</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>285352</t>
+          <t>283005</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>499463</t>
+          <t>499172</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>549559</t>
+          <t>550552</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55551</t>
+          <t>57061</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84674</t>
+          <t>85192</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72367</t>
+          <t>72265</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100703</t>
+          <t>101094</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>136582</t>
+          <t>137015</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178826</t>
+          <t>178271</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127944</t>
+          <t>127426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>157067</t>
+          <t>155557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>114485</t>
+          <t>114094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142821</t>
+          <t>142923</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248980</t>
+          <t>249535</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>291224</t>
+          <t>290791</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,97%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63818</t>
+          <t>63334</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93828</t>
+          <t>93081</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>95029</t>
+          <t>94955</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>127080</t>
+          <t>126508</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>166634</t>
+          <t>168355</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>210579</t>
+          <t>212632</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,56%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163581</t>
+          <t>164328</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193591</t>
+          <t>194075</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>127082</t>
+          <t>127654</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159133</t>
+          <t>159207</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>300992</t>
+          <t>298939</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>344937</t>
+          <t>343216</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,09%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>183673</t>
+          <t>183930</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>232890</t>
+          <t>232942</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>237054</t>
+          <t>236578</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>288626</t>
+          <t>290219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>435152</t>
+          <t>439257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>502425</t>
+          <t>504938</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>375232</t>
+          <t>375180</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>424449</t>
+          <t>424192</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>332420</t>
+          <t>330827</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>383992</t>
+          <t>384468</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>726743</t>
+          <t>724230</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>794016</t>
+          <t>789911</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,26%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>212120</t>
+          <t>210283</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>263196</t>
+          <t>270036</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>263993</t>
+          <t>265946</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>318706</t>
+          <t>321874</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>490855</t>
+          <t>491450</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>569108</t>
+          <t>569122</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>494681</t>
+          <t>487841</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>545757</t>
+          <t>547594</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>481690</t>
+          <t>478522</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>536403</t>
+          <t>534450</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>989165</t>
+          <t>989151</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1067418</t>
+          <t>1066823</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,46%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1030129</t>
+          <t>1027083</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1135805</t>
+          <t>1135492</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1249274</t>
+          <t>1240770</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1358923</t>
+          <t>1360887</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2301312</t>
+          <t>2297091</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2464960</t>
+          <t>2459735</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2144672</t>
+          <t>2144985</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2250348</t>
+          <t>2253394</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2003869</t>
+          <t>2001905</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2113518</t>
+          <t>2122022</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4178310</t>
+          <t>4183535</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4341958</t>
+          <t>4346179</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,9%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2016</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2016 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>74657</t>
+          <t>73048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107572</t>
+          <t>105861</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86658</t>
+          <t>86267</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118226</t>
+          <t>118360</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>166735</t>
+          <t>167977</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>215607</t>
+          <t>214585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,97%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>154785</t>
+          <t>156496</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>187700</t>
+          <t>189309</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143215</t>
+          <t>143081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174783</t>
+          <t>175174</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>308190</t>
+          <t>309212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>357062</t>
+          <t>355820</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,17%</t>
+          <t>67,93%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96536</t>
+          <t>95024</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>134522</t>
+          <t>132872</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145188</t>
+          <t>145953</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>187817</t>
+          <t>189474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>253278</t>
+          <t>253705</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>312114</t>
+          <t>312198</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>359248</t>
+          <t>360898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>397234</t>
+          <t>398746</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321186</t>
+          <t>319529</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363815</t>
+          <t>363050</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690659</t>
+          <t>690575</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>749495</t>
+          <t>749068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,7%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43040</t>
+          <t>44440</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69952</t>
+          <t>71115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32199</t>
+          <t>31522</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55812</t>
+          <t>56604</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>79961</t>
+          <t>82305</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116293</t>
+          <t>118237</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237669</t>
+          <t>236506</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>264581</t>
+          <t>263181</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>262768</t>
+          <t>261976</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286381</t>
+          <t>287058</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>509907</t>
+          <t>507963</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>546239</t>
+          <t>543895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>86,86%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81097</t>
+          <t>80898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>116554</t>
+          <t>115148</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>84682</t>
+          <t>85568</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>119864</t>
+          <t>121387</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>172857</t>
+          <t>176767</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>223473</t>
+          <t>226495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>222301</t>
+          <t>223707</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>257758</t>
+          <t>257957</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>231041</t>
+          <t>229518</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>266223</t>
+          <t>265337</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>466287</t>
+          <t>463265</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>516903</t>
+          <t>512993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,37%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41144</t>
+          <t>42199</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65275</t>
+          <t>67528</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35738</t>
+          <t>34641</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57779</t>
+          <t>57267</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81122</t>
+          <t>82181</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114875</t>
+          <t>116618</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129113</t>
+          <t>126860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>153244</t>
+          <t>152189</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>150591</t>
+          <t>151103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>172632</t>
+          <t>173729</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>287882</t>
+          <t>286139</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>321635</t>
+          <t>320576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,6%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44996</t>
+          <t>44132</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71269</t>
+          <t>70226</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>60233</t>
+          <t>59319</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88987</t>
+          <t>89235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112527</t>
+          <t>112121</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150273</t>
+          <t>150339</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168969</t>
+          <t>170012</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>195242</t>
+          <t>196106</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>157994</t>
+          <t>157746</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>186748</t>
+          <t>187662</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>336946</t>
+          <t>336880</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>374692</t>
+          <t>375098</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,99%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137510</t>
+          <t>137228</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>181655</t>
+          <t>181331</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164194</t>
+          <t>162619</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>212034</t>
+          <t>208655</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>310456</t>
+          <t>312628</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>376738</t>
+          <t>375837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,23%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>407972</t>
+          <t>408296</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>452117</t>
+          <t>452399</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,68%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>401908</t>
+          <t>405287</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>449748</t>
+          <t>451323</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>826831</t>
+          <t>827732</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>893113</t>
+          <t>890941</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,02%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>145428</t>
+          <t>146482</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>192113</t>
+          <t>192368</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>138616</t>
+          <t>138709</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>183929</t>
+          <t>184668</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>296013</t>
+          <t>293083</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>361919</t>
+          <t>362330</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>531974</t>
+          <t>531719</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>578659</t>
+          <t>577605</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>590188</t>
+          <t>589449</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>635501</t>
+          <t>635408</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1136285</t>
+          <t>1135874</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1202191</t>
+          <t>1205121</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>744248</t>
+          <t>747042</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>846071</t>
+          <t>847666</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>824932</t>
+          <t>822229</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>925972</t>
+          <t>926247</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1599733</t>
+          <t>1603052</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1747684</t>
+          <t>1748846</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2304871</t>
+          <t>2303276</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2406694</t>
+          <t>2403900</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2357365</t>
+          <t>2357090</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2458405</t>
+          <t>2461108</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4686595</t>
+          <t>4685433</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4834546</t>
+          <t>4831227</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>75,09%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2023</t>
+          <t>Población según si tienen algún familiar que fuma habitualmente en casa en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36480</t>
+          <t>37046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71615</t>
+          <t>70691</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46046</t>
+          <t>45189</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73204</t>
+          <t>71961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87894</t>
+          <t>88271</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>128624</t>
+          <t>131457</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>196814</t>
+          <t>197738</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>231949</t>
+          <t>231383</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179425</t>
+          <t>180668</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>206583</t>
+          <t>207440</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>392434</t>
+          <t>389601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>433164</t>
+          <t>432787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29244</t>
+          <t>30800</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75400</t>
+          <t>73502</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49521</t>
+          <t>47711</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75437</t>
+          <t>74767</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85933</t>
+          <t>84690</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136807</t>
+          <t>133815</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413913</t>
+          <t>415811</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>460069</t>
+          <t>458513</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>401086</t>
+          <t>401756</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>427002</t>
+          <t>428812</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>829029</t>
+          <t>832021</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>879903</t>
+          <t>881146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,23%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>12903</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29257</t>
+          <t>28372</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39122</t>
+          <t>38814</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63486</t>
+          <t>63363</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56499</t>
+          <t>57097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86368</t>
+          <t>85971</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>267464</t>
+          <t>268349</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283467</t>
+          <t>283818</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>259517</t>
+          <t>259640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>283881</t>
+          <t>284189</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>533356</t>
+          <t>533753</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>563225</t>
+          <t>562627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,79%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25151</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>57313</t>
+          <t>55412</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21829</t>
+          <t>23198</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56323</t>
+          <t>58281</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53643</t>
+          <t>56177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100467</t>
+          <t>107440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202552</t>
+          <t>204453</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>234714</t>
+          <t>235162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>360925</t>
+          <t>358967</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>395419</t>
+          <t>394050</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>576647</t>
+          <t>569674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>623471</t>
+          <t>620937</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,7%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3160</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14493</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8753</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18348</t>
+          <t>18099</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14179</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28769</t>
+          <t>28495</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>149935</t>
+          <t>150256</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161268</t>
+          <t>161611</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181741</t>
+          <t>181990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191327</t>
+          <t>191336</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>335748</t>
+          <t>336022</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>350338</t>
+          <t>350524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,16%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>17951</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37918</t>
+          <t>37702</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21285</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38875</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45655</t>
+          <t>44224</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72310</t>
+          <t>70906</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>211628</t>
+          <t>211844</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230633</t>
+          <t>231595</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>209327</t>
+          <t>209796</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226917</t>
+          <t>226469</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>425437</t>
+          <t>426841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>452092</t>
+          <t>453523</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>91002</t>
+          <t>94129</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139127</t>
+          <t>140249</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67132</t>
+          <t>65329</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>201991</t>
+          <t>202434</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>166761</t>
+          <t>163563</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>316094</t>
+          <t>318397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>447891</t>
+          <t>446769</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>496016</t>
+          <t>492889</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>619968</t>
+          <t>619525</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>754827</t>
+          <t>756630</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1092883</t>
+          <t>1090580</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1242216</t>
+          <t>1245414</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,39%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46153</t>
+          <t>44598</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>576702</t>
+          <t>594302</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28608</t>
+          <t>28498</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50315</t>
+          <t>50805</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>81341</t>
+          <t>84471</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>734377</t>
+          <t>846506</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>57,2%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>277958</t>
+          <t>260358</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>808507</t>
+          <t>810062</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>574830</t>
+          <t>574340</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>596537</t>
+          <t>596647</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>745427</t>
+          <t>633298</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1398463</t>
+          <t>1395333</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>362671</t>
+          <t>354939</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1220357</t>
+          <t>1164886</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>348927</t>
+          <t>344940</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>481007</t>
+          <t>485998</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>781055</t>
+          <t>776418</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1741870</t>
+          <t>1717584</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1949624</t>
+          <t>2005095</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2807310</t>
+          <t>2815042</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2883790</t>
+          <t>2878799</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3015870</t>
+          <t>3019857</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4792908</t>
+          <t>4817194</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5753723</t>
+          <t>5758360</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P26-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P26-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67728</t>
+          <t>66816</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96880</t>
+          <t>96550</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>84932</t>
+          <t>83148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115499</t>
+          <t>115064</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>158513</t>
+          <t>160623</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>202651</t>
+          <t>201742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,49%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>146719</t>
+          <t>147049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175871</t>
+          <t>176783</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115719</t>
+          <t>116154</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>146286</t>
+          <t>148070</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>272167</t>
+          <t>273076</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>316305</t>
+          <t>314195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,17%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100270</t>
+          <t>101038</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>137597</t>
+          <t>141104</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137490</t>
+          <t>136872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176753</t>
+          <t>174142</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>246619</t>
+          <t>244810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>302961</t>
+          <t>302416</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,51%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>330122</t>
+          <t>326615</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>367449</t>
+          <t>366681</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>285812</t>
+          <t>288423</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>325075</t>
+          <t>325693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>627323</t>
+          <t>627868</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>683665</t>
+          <t>685474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,68%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>66865</t>
+          <t>66690</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>97210</t>
+          <t>96211</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100651</t>
+          <t>99884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>134361</t>
+          <t>133469</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>175375</t>
+          <t>174842</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>220500</t>
+          <t>221348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,69%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>201266</t>
+          <t>202265</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>231611</t>
+          <t>231786</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170441</t>
+          <t>171333</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>204151</t>
+          <t>204918</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>382778</t>
+          <t>381930</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>427903</t>
+          <t>428436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80590</t>
+          <t>81600</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113919</t>
+          <t>112025</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126051</t>
+          <t>124996</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160352</t>
+          <t>160011</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>214589</t>
+          <t>216763</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>265910</t>
+          <t>266046</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225367</t>
+          <t>227261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>258696</t>
+          <t>257686</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>178926</t>
+          <t>179267</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>213227</t>
+          <t>214282</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>412653</t>
+          <t>412517</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>463974</t>
+          <t>461800</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,06%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39008</t>
+          <t>40037</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63376</t>
+          <t>64630</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44945</t>
+          <t>44445</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72442</t>
+          <t>70376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>90749</t>
+          <t>90435</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>126269</t>
+          <t>124259</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115886</t>
+          <t>114632</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>140254</t>
+          <t>139225</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>63,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115009</t>
+          <t>117075</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142506</t>
+          <t>143006</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>240444</t>
+          <t>242454</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275964</t>
+          <t>276278</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>56843</t>
+          <t>56441</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85124</t>
+          <t>85025</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83155</t>
+          <t>83239</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>112461</t>
+          <t>114216</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>148273</t>
+          <t>147748</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>186597</t>
+          <t>190687</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>165711</t>
+          <t>165810</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193992</t>
+          <t>194394</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>135446</t>
+          <t>133691</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>164752</t>
+          <t>164668</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>312146</t>
+          <t>308056</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>350470</t>
+          <t>350995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,38%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>153572</t>
+          <t>155123</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>198236</t>
+          <t>201490</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>203097</t>
+          <t>202239</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>250512</t>
+          <t>249880</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>369716</t>
+          <t>369035</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>437746</t>
+          <t>433051</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>378768</t>
+          <t>375514</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>423432</t>
+          <t>421881</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>337361</t>
+          <t>337993</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>384776</t>
+          <t>385634</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>727131</t>
+          <t>731826</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>795161</t>
+          <t>795842</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>174220</t>
+          <t>175762</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>224953</t>
+          <t>223515</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>226419</t>
+          <t>229176</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>280556</t>
+          <t>280698</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>415450</t>
+          <t>416469</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>486779</t>
+          <t>483064</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>470731</t>
+          <t>472169</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>521464</t>
+          <t>519922</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>450737</t>
+          <t>450595</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>504874</t>
+          <t>502117</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>940198</t>
+          <t>943913</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1011527</t>
+          <t>1010508</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>824973</t>
+          <t>818869</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>926295</t>
+          <t>923660</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1093745</t>
+          <t>1097897</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1202815</t>
+          <t>1201372</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1943490</t>
+          <t>1949927</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2096193</t>
+          <t>2091256</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2125571</t>
+          <t>2128206</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2226893</t>
+          <t>2232997</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1889572</t>
+          <t>1891015</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1998642</t>
+          <t>1994490</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4048060</t>
+          <t>4052997</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4200763</t>
+          <t>4194326</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91407</t>
+          <t>92677</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125762</t>
+          <t>126859</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100738</t>
+          <t>100522</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135562</t>
+          <t>136196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>200242</t>
+          <t>201394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>252208</t>
+          <t>249924</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,79%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>155157</t>
+          <t>154060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189512</t>
+          <t>188242</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141554</t>
+          <t>140920</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>176378</t>
+          <t>176594</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>305827</t>
+          <t>308111</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>357793</t>
+          <t>356641</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>63,91%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>138696</t>
+          <t>139866</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>185039</t>
+          <t>184337</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>187018</t>
+          <t>188089</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>234038</t>
+          <t>234729</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>341742</t>
+          <t>338558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>404881</t>
+          <t>401547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>39,98%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>308248</t>
+          <t>308950</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>354591</t>
+          <t>353421</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>276984</t>
+          <t>276293</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324004</t>
+          <t>322933</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>599428</t>
+          <t>602762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>662567</t>
+          <t>665751</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,29%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93215</t>
+          <t>93535</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125769</t>
+          <t>124932</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93523</t>
+          <t>93452</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126685</t>
+          <t>129060</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194692</t>
+          <t>193205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>241174</t>
+          <t>243040</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>177843</t>
+          <t>178680</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>210397</t>
+          <t>210077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>179685</t>
+          <t>177310</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>212847</t>
+          <t>212918</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>368808</t>
+          <t>366942</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>415290</t>
+          <t>416777</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,33%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89712</t>
+          <t>88310</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126622</t>
+          <t>125384</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94487</t>
+          <t>94582</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>130342</t>
+          <t>130467</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>193573</t>
+          <t>193823</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>244953</t>
+          <t>245952</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>240011</t>
+          <t>241249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276921</t>
+          <t>278323</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>247150</t>
+          <t>247025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>283005</t>
+          <t>282910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>499172</t>
+          <t>498173</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>550552</t>
+          <t>550302</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>57061</t>
+          <t>57047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85192</t>
+          <t>85814</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72265</t>
+          <t>73475</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>101094</t>
+          <t>102221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>137015</t>
+          <t>137758</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178271</t>
+          <t>178176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>127426</t>
+          <t>126804</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>155557</t>
+          <t>155571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>114094</t>
+          <t>112967</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142923</t>
+          <t>141713</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>249535</t>
+          <t>249630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>290791</t>
+          <t>290048</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63334</t>
+          <t>63326</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>93081</t>
+          <t>92851</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94955</t>
+          <t>94712</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>126508</t>
+          <t>127543</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>168355</t>
+          <t>166268</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>212632</t>
+          <t>209811</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,01%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>164328</t>
+          <t>164558</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>194075</t>
+          <t>194083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>127654</t>
+          <t>126619</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>159207</t>
+          <t>159450</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>298939</t>
+          <t>301760</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>343216</t>
+          <t>345303</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,5%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>183930</t>
+          <t>184543</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>232942</t>
+          <t>232837</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>236578</t>
+          <t>238865</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>290219</t>
+          <t>291622</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>439257</t>
+          <t>434258</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>504938</t>
+          <t>507092</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,25%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>375180</t>
+          <t>375285</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>424192</t>
+          <t>423579</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>330827</t>
+          <t>329424</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>384468</t>
+          <t>382181</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>724230</t>
+          <t>722076</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>789911</t>
+          <t>794910</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>64,67%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>210283</t>
+          <t>212455</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>270036</t>
+          <t>268025</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>265946</t>
+          <t>264936</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>321874</t>
+          <t>323395</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>491450</t>
+          <t>493001</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>569122</t>
+          <t>567366</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>487841</t>
+          <t>489852</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>547594</t>
+          <t>545422</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>478522</t>
+          <t>477001</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>534450</t>
+          <t>535460</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>989151</t>
+          <t>990907</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1066823</t>
+          <t>1065272</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1027083</t>
+          <t>1019908</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1135492</t>
+          <t>1131297</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1240770</t>
+          <t>1243776</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1360887</t>
+          <t>1360681</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2297091</t>
+          <t>2296675</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2459735</t>
+          <t>2459791</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2144985</t>
+          <t>2149180</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2253394</t>
+          <t>2260569</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2001905</t>
+          <t>2002111</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2122022</t>
+          <t>2119016</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4183535</t>
+          <t>4183479</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4346179</t>
+          <t>4346595</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73048</t>
+          <t>73700</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>105861</t>
+          <t>106204</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86267</t>
+          <t>87532</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>118360</t>
+          <t>118147</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>167977</t>
+          <t>170274</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>214585</t>
+          <t>215343</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>156496</t>
+          <t>156153</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189309</t>
+          <t>188657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143081</t>
+          <t>143294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>175174</t>
+          <t>173909</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>309212</t>
+          <t>308454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>355820</t>
+          <t>353523</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>67,49%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95024</t>
+          <t>94368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>132872</t>
+          <t>133833</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145953</t>
+          <t>146322</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>189474</t>
+          <t>190840</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>253705</t>
+          <t>253179</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>312198</t>
+          <t>309873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>360898</t>
+          <t>359937</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>398746</t>
+          <t>399402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>319529</t>
+          <t>318163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363050</t>
+          <t>362681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>690575</t>
+          <t>692900</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>749068</t>
+          <t>749594</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,75%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44440</t>
+          <t>44023</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71115</t>
+          <t>68720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31522</t>
+          <t>30611</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56604</t>
+          <t>56277</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82305</t>
+          <t>82052</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>118237</t>
+          <t>117418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>236506</t>
+          <t>238901</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>263181</t>
+          <t>263598</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>261976</t>
+          <t>262303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>287058</t>
+          <t>287969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>507963</t>
+          <t>508782</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>543895</t>
+          <t>544148</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>80898</t>
+          <t>82978</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115148</t>
+          <t>117322</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85568</t>
+          <t>85612</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121387</t>
+          <t>120425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176767</t>
+          <t>175385</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>226495</t>
+          <t>224205</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>223707</t>
+          <t>221533</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>257957</t>
+          <t>255877</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>229518</t>
+          <t>230480</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>265337</t>
+          <t>265293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>463265</t>
+          <t>465555</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>512993</t>
+          <t>514375</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,57%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42199</t>
+          <t>42904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67528</t>
+          <t>66797</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34641</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57267</t>
+          <t>58368</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82181</t>
+          <t>83402</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>116618</t>
+          <t>116691</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>126860</t>
+          <t>127591</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152189</t>
+          <t>151484</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>151103</t>
+          <t>150002</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>173729</t>
+          <t>172862</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>286139</t>
+          <t>286066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>320576</t>
+          <t>319355</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>71,04%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44132</t>
+          <t>44411</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70226</t>
+          <t>70562</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59319</t>
+          <t>58633</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89235</t>
+          <t>89191</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112121</t>
+          <t>112669</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150339</t>
+          <t>150585</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,91%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170012</t>
+          <t>169676</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>196106</t>
+          <t>195827</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>157746</t>
+          <t>157790</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>187662</t>
+          <t>188348</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>336880</t>
+          <t>336634</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>375098</t>
+          <t>374550</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,88%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137228</t>
+          <t>137956</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>181331</t>
+          <t>184945</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>162619</t>
+          <t>164021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>208655</t>
+          <t>208341</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>312628</t>
+          <t>313709</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>375837</t>
+          <t>377433</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>408296</t>
+          <t>404682</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>452399</t>
+          <t>451671</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>405287</t>
+          <t>405601</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>451323</t>
+          <t>449921</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>827732</t>
+          <t>826136</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>890941</t>
+          <t>889860</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,94%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>146482</t>
+          <t>146560</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>192368</t>
+          <t>192863</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>138709</t>
+          <t>136053</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>184668</t>
+          <t>184222</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>293083</t>
+          <t>298424</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>362330</t>
+          <t>360080</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>531719</t>
+          <t>531224</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>577605</t>
+          <t>577527</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>589449</t>
+          <t>589895</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>635408</t>
+          <t>638064</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1135874</t>
+          <t>1138124</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1205121</t>
+          <t>1199780</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,08%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>747042</t>
+          <t>747300</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>847666</t>
+          <t>845332</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>822229</t>
+          <t>828639</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>926247</t>
+          <t>927472</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1603052</t>
+          <t>1604204</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1748846</t>
+          <t>1744154</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2303276</t>
+          <t>2305610</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2403900</t>
+          <t>2403642</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2357090</t>
+          <t>2355865</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2461108</t>
+          <t>2454698</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4685433</t>
+          <t>4690125</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4831227</t>
+          <t>4830075</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>50887</t>
+          <t>46051</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37046</t>
+          <t>33850</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70691</t>
+          <t>61193</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>56707</t>
+          <t>56762</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45189</t>
+          <t>45590</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71961</t>
+          <t>69857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>107594</t>
+          <t>102813</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88271</t>
+          <t>86014</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131457</t>
+          <t>121783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>217542</t>
+          <t>231338</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>197738</t>
+          <t>216196</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>231383</t>
+          <t>243539</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>195922</t>
+          <t>219240</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>180668</t>
+          <t>206145</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>207440</t>
+          <t>230412</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>413464</t>
+          <t>450578</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>389601</t>
+          <t>431608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>432787</t>
+          <t>467377</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>84,46%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>268429</t>
+          <t>277389</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>268429</t>
+          <t>277389</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>268429</t>
+          <t>277389</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>252629</t>
+          <t>276002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>252629</t>
+          <t>276002</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>252629</t>
+          <t>276002</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>521058</t>
+          <t>553391</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>521058</t>
+          <t>553391</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>521058</t>
+          <t>553391</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48720</t>
+          <t>46534</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30800</t>
+          <t>29150</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73502</t>
+          <t>71946</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>60527</t>
+          <t>62355</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47711</t>
+          <t>48532</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74767</t>
+          <t>78121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>109247</t>
+          <t>108890</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84690</t>
+          <t>86533</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133815</t>
+          <t>136278</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>440593</t>
+          <t>452813</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>415811</t>
+          <t>427401</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>458513</t>
+          <t>470197</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>415996</t>
+          <t>444578</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>401756</t>
+          <t>428812</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>428812</t>
+          <t>458401</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>856589</t>
+          <t>897391</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>832021</t>
+          <t>870003</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>881146</t>
+          <t>919748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>489313</t>
+          <t>499347</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>489313</t>
+          <t>499347</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>489313</t>
+          <t>499347</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>476523</t>
+          <t>506933</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>476523</t>
+          <t>506933</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>476523</t>
+          <t>506933</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>965836</t>
+          <t>1006281</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>965836</t>
+          <t>1006281</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>965836</t>
+          <t>1006281</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>23366</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12903</t>
+          <t>15193</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28372</t>
+          <t>33540</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>50139</t>
+          <t>50247</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38814</t>
+          <t>39373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>63363</t>
+          <t>62154</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>69820</t>
+          <t>73613</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57097</t>
+          <t>59258</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85971</t>
+          <t>88250</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>277040</t>
+          <t>272754</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>268349</t>
+          <t>262580</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>283818</t>
+          <t>280927</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>272864</t>
+          <t>279533</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>259640</t>
+          <t>267626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>284189</t>
+          <t>290407</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>549904</t>
+          <t>552287</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>533753</t>
+          <t>537650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>562627</t>
+          <t>566642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>296721</t>
+          <t>296120</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>296721</t>
+          <t>296120</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>296721</t>
+          <t>296120</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>323003</t>
+          <t>329780</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>323003</t>
+          <t>329780</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>323003</t>
+          <t>329780</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>619724</t>
+          <t>625900</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>619724</t>
+          <t>625900</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>619724</t>
+          <t>625900</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38153</t>
+          <t>43869</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24703</t>
+          <t>28322</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55412</t>
+          <t>64012</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40046</t>
+          <t>46371</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23198</t>
+          <t>35317</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58281</t>
+          <t>61915</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>78199</t>
+          <t>90240</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>56177</t>
+          <t>71007</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107440</t>
+          <t>113344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>221712</t>
+          <t>260540</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>204453</t>
+          <t>240397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235162</t>
+          <t>276087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>377202</t>
+          <t>312506</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>358967</t>
+          <t>296962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>394050</t>
+          <t>323560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>598915</t>
+          <t>573045</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>569674</t>
+          <t>549941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>620937</t>
+          <t>592278</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>89,29%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>259865</t>
+          <t>304409</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>259865</t>
+          <t>304409</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>259865</t>
+          <t>304409</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>417248</t>
+          <t>358877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>417248</t>
+          <t>358877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>417248</t>
+          <t>358877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>677114</t>
+          <t>663285</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>677114</t>
+          <t>663285</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>677114</t>
+          <t>663285</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>9535</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>17461</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>13834</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8753</t>
+          <t>9633</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>20073</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13993</t>
+          <t>16707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28495</t>
+          <t>32326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>157379</t>
+          <t>180024</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150256</t>
+          <t>172098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161611</t>
+          <t>184774</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>187065</t>
+          <t>205556</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181990</t>
+          <t>199312</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191336</t>
+          <t>209757</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>344444</t>
+          <t>385580</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>336022</t>
+          <t>376623</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>350524</t>
+          <t>392242</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>164428</t>
+          <t>189559</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164428</t>
+          <t>189559</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>164428</t>
+          <t>189559</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>200089</t>
+          <t>219390</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>200089</t>
+          <t>219390</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>200089</t>
+          <t>219390</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>364517</t>
+          <t>408949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>364517</t>
+          <t>408949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>364517</t>
+          <t>408949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>27453</t>
+          <t>28649</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37702</t>
+          <t>39312</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29405</t>
+          <t>29067</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21733</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>38979</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>56858</t>
+          <t>57716</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44224</t>
+          <t>46924</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70906</t>
+          <t>71661</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>222093</t>
+          <t>222609</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>211844</t>
+          <t>211946</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>231595</t>
+          <t>230894</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>218797</t>
+          <t>225479</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>209796</t>
+          <t>215567</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>226469</t>
+          <t>233745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>440889</t>
+          <t>448087</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>426841</t>
+          <t>434142</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>453523</t>
+          <t>458879</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>249546</t>
+          <t>251258</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>249546</t>
+          <t>251258</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>249546</t>
+          <t>251258</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>248202</t>
+          <t>254546</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>248202</t>
+          <t>254546</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>248202</t>
+          <t>254546</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>497747</t>
+          <t>505803</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>497747</t>
+          <t>505803</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>497747</t>
+          <t>505803</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>113730</t>
+          <t>127406</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94129</t>
+          <t>105301</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>140249</t>
+          <t>153844</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>145531</t>
+          <t>166494</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65329</t>
+          <t>145907</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>202434</t>
+          <t>189131</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>259260</t>
+          <t>293901</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>163563</t>
+          <t>261735</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>318397</t>
+          <t>333233</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>473288</t>
+          <t>545802</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>446769</t>
+          <t>519364</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>492889</t>
+          <t>567907</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>676428</t>
+          <t>572383</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>619525</t>
+          <t>549746</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>756630</t>
+          <t>592970</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1149717</t>
+          <t>1118184</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1090580</t>
+          <t>1078852</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1245414</t>
+          <t>1150350</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>587018</t>
+          <t>673208</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>587018</t>
+          <t>673208</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>587018</t>
+          <t>673208</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>821959</t>
+          <t>738877</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>821959</t>
+          <t>738877</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>821959</t>
+          <t>738877</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1408977</t>
+          <t>1412085</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1408977</t>
+          <t>1412085</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1408977</t>
+          <t>1412085</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>280587</t>
+          <t>40977</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44598</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>594302</t>
+          <t>58246</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>38013</t>
+          <t>42451</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28498</t>
+          <t>31917</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50805</t>
+          <t>55585</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>318599</t>
+          <t>83428</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>84471</t>
+          <t>66088</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>846506</t>
+          <t>104079</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>574073</t>
+          <t>666905</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>260358</t>
+          <t>649636</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>810062</t>
+          <t>678886</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>587132</t>
+          <t>682446</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>574340</t>
+          <t>669312</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>596647</t>
+          <t>692980</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1161205</t>
+          <t>1349352</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>633298</t>
+          <t>1328701</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1395333</t>
+          <t>1366692</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>854660</t>
+          <t>707882</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>854660</t>
+          <t>707882</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>854660</t>
+          <t>707882</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>625145</t>
+          <t>724897</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>625145</t>
+          <t>724897</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>625145</t>
+          <t>724897</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1479804</t>
+          <t>1432780</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1479804</t>
+          <t>1432780</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1479804</t>
+          <t>1432780</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>586260</t>
+          <t>366387</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>354939</t>
+          <t>326728</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1164886</t>
+          <t>413423</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>433391</t>
+          <t>467580</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>344940</t>
+          <t>429704</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>485998</t>
+          <t>505219</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1019650</t>
+          <t>833968</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>776418</t>
+          <t>778596</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1717584</t>
+          <t>892654</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2583721</t>
+          <t>2832785</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2005095</t>
+          <t>2785749</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2815042</t>
+          <t>2872444</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>87,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2931406</t>
+          <t>2941722</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2878799</t>
+          <t>2904083</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3019857</t>
+          <t>2979598</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5515128</t>
+          <t>5774506</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4817194</t>
+          <t>5715820</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5758360</t>
+          <t>5829878</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,22%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3169981</t>
+          <t>3199172</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3169981</t>
+          <t>3199172</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3169981</t>
+          <t>3199172</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3364797</t>
+          <t>3409302</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3364797</t>
+          <t>3409302</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3364797</t>
+          <t>3409302</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6534778</t>
+          <t>6608474</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6534778</t>
+          <t>6608474</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6534778</t>
+          <t>6608474</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
